--- a/MyStore bug report.xlsx
+++ b/MyStore bug report.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyStoreTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABCF6883-BE83-45E5-A7E2-9355C455D97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881EB6F8-9108-4910-8129-81FE7131C269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9079AC35-1039-4AD3-A36E-21083BC5FBB0}"/>
   </bookViews>
   <sheets>
     <sheet name="buig 3(1)" sheetId="5" r:id="rId1"/>
-    <sheet name="buig 2" sheetId="4" r:id="rId2"/>
+    <sheet name="buig 2" sheetId="4" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t xml:space="preserve">name </t>
   </si>
@@ -169,6 +169,27 @@
   </si>
   <si>
     <t>go to the Checkout page to complete payment process</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Login/ SignUp</t>
+  </si>
+  <si>
+    <t>Input Data For Login and SignUp Pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">after after sign up or login , the site should  send message as successfully registration </t>
+  </si>
+  <si>
+    <t>the site stay in the same page without send any message or navigate to the second page</t>
+  </si>
+  <si>
+    <t>after sign up the site should send message as successfully registration and navigate me to Login Page</t>
+  </si>
+  <si>
+    <t>High---&gt;&gt; Users don't know if process success or note</t>
   </si>
 </sst>
 </file>
@@ -634,16 +655,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E4D1FDA-8B77-47CF-B8C3-0C7F18D5163B}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="26.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.28515625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="4" width="82.7109375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>14</v>
       </c>
@@ -653,8 +674,11 @@
       <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -662,8 +686,11 @@
       <c r="C2" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -671,8 +698,11 @@
       <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="1" t="s">
         <v>10</v>
@@ -680,8 +710,11 @@
       <c r="C4" s="4">
         <v>46057</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -689,8 +722,9 @@
         <v>11</v>
       </c>
       <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
@@ -700,8 +734,11 @@
       <c r="C6" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
@@ -711,8 +748,11 @@
       <c r="C7" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>3</v>
@@ -720,8 +760,11 @@
       <c r="C8" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.25">
+      <c r="D8" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="1" t="s">
         <v>8</v>
@@ -729,8 +772,11 @@
       <c r="C9" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="36" x14ac:dyDescent="0.25">
+      <c r="D9" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
@@ -738,8 +784,11 @@
       <c r="C10" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>18</v>
       </c>
@@ -749,14 +798,17 @@
       <c r="C11" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="1" t="s">
         <v>1</v>
@@ -764,12 +816,16 @@
       <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
